--- a/site/iCIMS-Payworks-Integration-Guide/headings.xlsx
+++ b/site/iCIMS-Payworks-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Key Functions</t>
+          <t>Key Functions - To be checked later</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Overview Tab</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,41 +539,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01M48R05FPQXM954YJC5JBXDXN</t>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPQXM954YJC5JBXDXN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01M48R05FPVKN038ZENHVAYS0J</t>
+          <t>h_01M48R05FPQXM954YJC5JBXDXN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPVKN038ZENHVAYS0J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPQXM954YJC5JBXDXN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Connections</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,41 +583,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01M48R05FPG2E7FXFHBVX30WQZ</t>
+          <t>h_01M48R05FPVKN038ZENHVAYS0J</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPG2E7FXFHBVX30WQZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPVKN038ZENHVAYS0J</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sync Control Settings</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01M48R05FP0A6SW8SBM66GC2KD</t>
+          <t>h_01M48R05FPG2E7FXFHBVX30WQZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP0A6SW8SBM66GC2KD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPG2E7FXFHBVX30WQZ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Operational Features</t>
+          <t>Sync Control Settings / Synchronization settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01M48R05FPT8VKY52WQXCVB9KM</t>
+          <t>h_01M48R05FP0A6SW8SBM66GC2KD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPT8VKY52WQXCVB9KM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP0A6SW8SBM66GC2KD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manual Candidate Run</t>
+          <t>Operational Features / Operational settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,63 +649,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01M48R05FPHERSA56FV83CZSF3</t>
+          <t>h_01M48R05FPT8VKY52WQXCVB9KM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPHERSA56FV83CZSF3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPT8VKY52WQXCVB9KM</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iCIMS to Payworks Tab</t>
+          <t>Manual Candidate Run / Manual candidate execution</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>icims-to-payworks-tab</t>
+          <t>h_01M48R05FPHERSA56FV83CZSF3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#icims-to-payworks-tab</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPHERSA56FV83CZSF3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iCIMS Settings</t>
+          <t>iCIMS to Payworks</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01M48R05FPC38KK7JKBYB89VGS</t>
+          <t>icims-to-payworks-tab</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPC38KK7JKBYB89VGS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#icims-to-payworks-tab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Payworks Settings</t>
+          <t>iCIMS Settings / iCIMS settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01M48R05FP92JB0F1JJA5QD1KW</t>
+          <t>h_01M48R05FPC38KK7JKBYB89VGS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP92JB0F1JJA5QD1KW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPC38KK7JKBYB89VGS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lifecycle Operations</t>
+          <t>Payworks Settings / Payworks settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01M48R05FPMY3VTP0EC0E647D8</t>
+          <t>h_01M48R05FP92JB0F1JJA5QD1KW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPMY3VTP0EC0E647D8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP92JB0F1JJA5QD1KW</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Create Settings</t>
+          <t>Lifecycle Operations / Lifecycle operations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,129 +759,129 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01M48R05FPDTV0HE6VR6P67NZ7</t>
+          <t>h_01M48R05FPMY3VTP0EC0E647D8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPDTV0HE6VR6P67NZ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPMY3VTP0EC0E647D8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Update Settings</t>
+          <t>Create Settings / Create settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01M48R05FP95ADSZM9G81G4XC9</t>
+          <t>h_01M48R05FPDTV0HE6VR6P67NZ7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP95ADSZM9G81G4XC9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPDTV0HE6VR6P67NZ7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Delete Settings</t>
+          <t>Update Settings / Update settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01M48R05FPN105671622YPYTGP</t>
+          <t>h_01M48R05FP95ADSZM9G81G4XC9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPN105671622YPYTGP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP95ADSZM9G81G4XC9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Employee Record Steps</t>
+          <t>Delete Settings / Delete settings -  can we say termination??</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01M48R05FP7KATAGXMND4F8F7Y</t>
+          <t>h_01M48R05FPN105671622YPYTGP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP7KATAGXMND4F8F7Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPN105671622YPYTGP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Payworks to iCIMS Tab</t>
+          <t>Employee Record Steps / Employee record settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01M48R05FPQR1GY13ES74NJJMK</t>
+          <t>h_01M48R05FP7KATAGXMND4F8F7Y</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPQR1GY13ES74NJJMK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP7KATAGXMND4F8F7Y</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iCIMS Settings</t>
+          <t>Payworks to iCIMS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01M48R05FPPQ5JZJGXMRKC8JV0</t>
+          <t>h_01M48R05FPQR1GY13ES74NJJMK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPPQ5JZJGXMRKC8JV0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPQR1GY13ES74NJJMK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Payworks Settings</t>
+          <t>iCIMS Settings / iCIMS settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01M48R05FP7G1E87TWPBPBMG17</t>
+          <t>h_01M48R05FPPQ5JZJGXMRKC8JV0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP7G1E87TWPBPBMG17</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPPQ5JZJGXMRKC8JV0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lifecycle Operations</t>
+          <t>Payworks Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,63 +913,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01M48R05FPD2VD7SK2PN3A5RDP</t>
+          <t>h_01M48R05FP7G1E87TWPBPBMG17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPD2VD7SK2PN3A5RDP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP7G1E87TWPBPBMG17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Operation Settings Tab</t>
+          <t>Lifecycle Operations / Lifecycle operations</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01M48R05FPD9W3SZ5KZF0CPTA8</t>
+          <t>h_01M48R05FPD2VD7SK2PN3A5RDP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPD9W3SZ5KZF0CPTA8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPD2VD7SK2PN3A5RDP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Operation Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01M48R05FP9703BS60A5VTEW1D</t>
+          <t>h_01M48R05FPD9W3SZ5KZF0CPTA8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9703BS60A5VTEW1D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPD9W3SZ5KZF0CPTA8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01M48R05FPSGZE8V5M1N5JYRX1</t>
+          <t>h_01M48R05FP9703BS60A5VTEW1D</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPSGZE8V5M1N5JYRX1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9703BS60A5VTEW1D</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Advance Settings</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01M48R05FPVMH5RWRSASM3MAC2</t>
+          <t>h_01M48R05FPSGZE8V5M1N5JYRX1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPVMH5RWRSASM3MAC2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPSGZE8V5M1N5JYRX1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Advance Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,63 +1023,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01M48R05FPN1C8H3Z0EG6JZWZB</t>
+          <t>h_01M48R05FPVMH5RWRSASM3MAC2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPN1C8H3Z0EG6JZWZB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPVMH5RWRSASM3MAC2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Notification Tab</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01M48R05FPDFTVZS6H949Z2VCG</t>
+          <t>h_01M48R05FPN1C8H3Z0EG6JZWZB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPDFTVZS6H949Z2VCG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPN1C8H3Z0EG6JZWZB</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification Recipients</t>
+          <t>Notification Tab</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01M48R05FP6MN05YYP8MG2KG3T</t>
+          <t>h_01M48R05FPDFTVZS6H949Z2VCG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP6MN05YYP8MG2KG3T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPDFTVZS6H949Z2VCG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Execution Success Notification</t>
+          <t>Notification Recipients</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01M48R05FPPF5PAN8A4S7FWR7F</t>
+          <t>h_01M48R05FP6MN05YYP8MG2KG3T</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPPF5PAN8A4S7FWR7F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP6MN05YYP8MG2KG3T</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execution Failure Notification</t>
+          <t>Execution Success Notification</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01M48R05FPJ6SPSXWAA2DRWVZ5</t>
+          <t>h_01M48R05FPPF5PAN8A4S7FWR7F</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPJ6SPSXWAA2DRWVZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPPF5PAN8A4S7FWR7F</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Execution Failure Notification</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,41 +1133,41 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01M48R05FPXFTG2516K5XWZB4E</t>
+          <t>h_01M48R05FPJ6SPSXWAA2DRWVZ5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPXFTG2516K5XWZB4E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPJ6SPSXWAA2DRWVZ5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Attribute Mapper Tab</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01M48R05FP913PY6SJYBQN5DTH</t>
+          <t>h_01M48R05FPXFTG2516K5XWZB4E</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP913PY6SJYBQN5DTH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPXFTG2516K5XWZB4E</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tables Tab</t>
+          <t>Attribute Mapper Tab</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,19 +1177,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01M48R05FPZWY49H4T0KDV19DA</t>
+          <t>h_01M48R05FP913PY6SJYBQN5DTH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPZWY49H4T0KDV19DA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP913PY6SJYBQN5DTH</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Schedule Tab</t>
+          <t>Tables Tab</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,63 +1199,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01M48R05FPPEFT08NGB5Y5MBP5</t>
+          <t>h_01M48R05FPZWY49H4T0KDV19DA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPPEFT08NGB5Y5MBP5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPZWY49H4T0KDV19DA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>How the Integration Processes Records</t>
+          <t>Schedule Tab</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01M48R05FP9MD4T960YT733EXA</t>
+          <t>h_01M48R05FPPEFT08NGB5Y5MBP5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9MD4T960YT733EXA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPPEFT08NGB5Y5MBP5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iCIMS to Payworks</t>
+          <t>How the Integration Processes Records</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01M48R05FPQTH7V0W5HC48KTQS</t>
+          <t>h_01M48R05FP9MD4T960YT733EXA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPQTH7V0W5HC48KTQS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9MD4T960YT733EXA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Payworks to iCIMS</t>
+          <t>iCIMS to Payworks</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1265,19 +1265,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01M48R05FP598Z3MNZWH83ZQQ0</t>
+          <t>h_01M48R05FPQTH7V0W5HC48KTQS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP598Z3MNZWH83ZQQ0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPQTH7V0W5HC48KTQS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Correlation</t>
+          <t>Payworks to iCIMS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,19 +1287,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01M48R05FPYJEE7WSTBWCZ6PY0</t>
+          <t>h_01M48R05FP598Z3MNZWH83ZQQ0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPYJEE7WSTBWCZ6PY0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP598Z3MNZWH83ZQQ0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Retries and Idempotency</t>
+          <t>Correlation</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,32 +1309,54 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01M48R05FP9824F2K3W9Y4GYHA</t>
+          <t>h_01M48R05FPYJEE7WSTBWCZ6PY0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9824F2K3W9Y4GYHA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPYJEE7WSTBWCZ6PY0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Retries and Idempotency</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01M48R05FP9824F2K3W9Y4GYHA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9824F2K3W9Y4GYHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>PII Masking</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>h_01M48R05FPJ9HTT5Y3EBTZ2RKJ</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPJ9HTT5Y3EBTZ2RKJ</t>
         </is>

--- a/site/iCIMS-Payworks-Integration-Guide/headings.xlsx
+++ b/site/iCIMS-Payworks-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manual Candidate Run / Manual candidate execution</t>
+          <t>Manual Candidate Run / Manual candidate execution - Should it move under iCIMS to Payworks tab?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Delete Settings / Delete settings -  can we say termination??</t>
+          <t>Delete Settings / Termination settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Payworks Settings</t>
+          <t>Payworks Settings / Payworks settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -947,95 +947,95 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Operation Settings</t>
+          <t>Create Settings / Create settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01M48R05FPD9W3SZ5KZF0CPTA8</t>
+          <t>h_01M4X05BTQ97RBJ3QKR9H46W76</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPD9W3SZ5KZF0CPTA8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4X05BTQ97RBJ3QKR9H46W76</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Update Settings / Update settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01M48R05FP9703BS60A5VTEW1D</t>
+          <t>h_01M4X05BTQY71V6D2YGQS1FHT9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9703BS60A5VTEW1D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4X05BTQY71V6D2YGQS1FHT9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Delete Settings / Termination settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01M48R05FPSGZE8V5M1N5JYRX1</t>
+          <t>h_01M4X05BTQRWVPM62M12GM17CT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPSGZE8V5M1N5JYRX1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4X05BTQRWVPM62M12GM17CT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Advance Settings</t>
+          <t>Operation Settings / Operation settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01M48R05FPVMH5RWRSASM3MAC2</t>
+          <t>h_01M48R05FPD9W3SZ5KZF0CPTA8</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPVMH5RWRSASM3MAC2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPD9W3SZ5KZF0CPTA8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Log Settings / Log settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,41 +1045,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01M48R05FPN1C8H3Z0EG6JZWZB</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPN1C8H3Z0EG6JZWZB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification Tab</t>
+          <t>Report Settings / Report settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01M48R05FPDFTVZS6H949Z2VCG</t>
+          <t>h_01M48R05FPSGZE8V5M1N5JYRX1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPDFTVZS6H949Z2VCG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPSGZE8V5M1N5JYRX1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Notification Recipients</t>
+          <t>Advance Settings / Advanced settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,63 +1089,63 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01M48R05FP6MN05YYP8MG2KG3T</t>
+          <t>h_01M48R05FPVMH5RWRSASM3MAC2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP6MN05YYP8MG2KG3T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPVMH5RWRSASM3MAC2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execution Success Notification</t>
+          <t>PII &amp; Security / Data protection</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01M48R05FPPF5PAN8A4S7FWR7F</t>
+          <t>h_01M4WWV2K0B3EDXTQZRMAV8B4T</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPPF5PAN8A4S7FWR7F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4WWV2K0B3EDXTQZRMAV8B4T</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Execution Failure Notification</t>
+          <t>Settings / Retry settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01M48R05FPJ6SPSXWAA2DRWVZ5</t>
+          <t>h_01M4WWV6EH1N0VJ0NRKE5FZ46M</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPJ6SPSXWAA2DRWVZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4WWV6EH1N0VJ0NRKE5FZ46M</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01M48R05FPXFTG2516K5XWZB4E</t>
+          <t>h_01M48R05FPN1C8H3Z0EG6JZWZB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPXFTG2516K5XWZB4E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPN1C8H3Z0EG6JZWZB</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Attribute Mapper Tab</t>
+          <t>Notification Tab</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,107 +1177,107 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01M48R05FP913PY6SJYBQN5DTH</t>
+          <t>h_01M48R05FPDFTVZS6H949Z2VCG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP913PY6SJYBQN5DTH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPDFTVZS6H949Z2VCG</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tables Tab</t>
+          <t>Notification Recipients</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01M48R05FPZWY49H4T0KDV19DA</t>
+          <t>h_01M48R05FP6MN05YYP8MG2KG3T</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPZWY49H4T0KDV19DA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP6MN05YYP8MG2KG3T</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Schedule Tab</t>
+          <t>Execution Success Notification</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01M48R05FPPEFT08NGB5Y5MBP5</t>
+          <t>h_01M48R05FPPF5PAN8A4S7FWR7F</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPPEFT08NGB5Y5MBP5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPPF5PAN8A4S7FWR7F</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>How the Integration Processes Records</t>
+          <t>Execution Failure Notification</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01M48R05FP9MD4T960YT733EXA</t>
+          <t>h_01M48R05FPJ6SPSXWAA2DRWVZ5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9MD4T960YT733EXA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPJ6SPSXWAA2DRWVZ5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>iCIMS to Payworks</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01M48R05FPQTH7V0W5HC48KTQS</t>
+          <t>h_01M48R05FPXFTG2516K5XWZB4E</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPQTH7V0W5HC48KTQS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPXFTG2516K5XWZB4E</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Payworks to iCIMS</t>
+          <t>Attribute Mapper</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,19 +1287,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01M48R05FP598Z3MNZWH83ZQQ0</t>
+          <t>h_01M48R05FP913PY6SJYBQN5DTH</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP598Z3MNZWH83ZQQ0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP913PY6SJYBQN5DTH</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Correlation</t>
+          <t>Tables Tab</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,19 +1309,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01M48R05FPYJEE7WSTBWCZ6PY0</t>
+          <t>h_01M48R05FPZWY49H4T0KDV19DA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPYJEE7WSTBWCZ6PY0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPZWY49H4T0KDV19DA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Retries and Idempotency</t>
+          <t>Schedule Tab</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1331,32 +1331,142 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01M48R05FP9824F2K3W9Y4GYHA</t>
+          <t>h_01M48R05FPPEFT08NGB5Y5MBP5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9824F2K3W9Y4GYHA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPPEFT08NGB5Y5MBP5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>How the Integration Processes Records</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01M48R05FP9MD4T960YT733EXA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9MD4T960YT733EXA</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>iCIMS to Payworks</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01M48R05FPQTH7V0W5HC48KTQS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPQTH7V0W5HC48KTQS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Payworks to iCIMS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01M48R05FP598Z3MNZWH83ZQQ0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP598Z3MNZWH83ZQQ0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Correlation</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01M48R05FPYJEE7WSTBWCZ6PY0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPYJEE7WSTBWCZ6PY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Retries and Idempotency</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01M48R05FP9824F2K3W9Y4GYHA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9824F2K3W9Y4GYHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>PII Masking</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>h_01M48R05FPJ9HTT5Y3EBTZ2RKJ</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPJ9HTT5Y3EBTZ2RKJ</t>
         </is>

--- a/site/iCIMS-Payworks-Integration-Guide/headings.xlsx
+++ b/site/iCIMS-Payworks-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Key Functions - To be checked later</t>
+          <t>Key Functions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01M4X05BTQ97RBJ3QKR9H46W76</t>
+          <t>h_01M4X9TQ6SZVKPX81A62JV55MR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4X05BTQ97RBJ3QKR9H46W76</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4X9TQ6SZVKPX81A62JV55MR</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01M4X05BTQY71V6D2YGQS1FHT9</t>
+          <t>h_01M4X9TQ6SGAMPDX4GMF59KQHC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4X05BTQY71V6D2YGQS1FHT9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4X9TQ6SGAMPDX4GMF59KQHC</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01M4X05BTQRWVPM62M12GM17CT</t>
+          <t>h_01M4X9TQ6SZE5T5ASNEEPK0YND</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4X05BTQRWVPM62M12GM17CT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M4X9TQ6SZE5T5ASNEEPK0YND</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Notification Tab</t>
+          <t>Notification / Notifications</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Notification Recipients</t>
+          <t>Notification Recipients / Notification recipients</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Execution Success Notification</t>
+          <t>Execution Success Notification / Execution success notification</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Execution Failure Notification</t>
+          <t>Execution Failure Notification / Execution failure notification</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Notification Report Settings / Notification report settings</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tables Tab</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Schedule Tab</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>How the Integration Processes Records</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,122 +1353,34 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01M48R05FP9MD4T960YT733EXA</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9MD4T960YT733EXA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iCIMS to Payworks</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01M48R05FPQTH7V0W5HC48KTQS</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPQTH7V0W5HC48KTQS</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Payworks to iCIMS</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>h_01M48R05FP598Z3MNZWH83ZQQ0</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP598Z3MNZWH83ZQQ0</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Correlation</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>h_01M48R05FPYJEE7WSTBWCZ6PY0</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPYJEE7WSTBWCZ6PY0</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Retries and Idempotency</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>h_01M48R05FP9824F2K3W9Y4GYHA</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FP9824F2K3W9Y4GYHA</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>PII Masking</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>h_01M48R05FPJ9HTT5Y3EBTZ2RKJ</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01M48R05FPJ9HTT5Y3EBTZ2RKJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/iCIMS-Payworks-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>

--- a/site/iCIMS-Payworks-Integration-Guide/headings.xlsx
+++ b/site/iCIMS-Payworks-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sync Control Settings / Synchronization settings</t>
+          <t>Synchronization settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Operational Features / Operational settings</t>
+          <t>Operational settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manual Candidate Run / Manual candidate execution - Should it move under iCIMS to Payworks tab?</t>
+          <t>Manual candidate execution</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iCIMS Settings / iCIMS settings</t>
+          <t>iCIMS settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Payworks Settings / Payworks settings</t>
+          <t>Payworks settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lifecycle Operations / Lifecycle operations</t>
+          <t>Lifecycle operations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Create Settings / Create settings</t>
+          <t>Create settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Update Settings / Update settings</t>
+          <t>Update settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Delete Settings / Termination settings</t>
+          <t>Termination settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Employee Record Steps / Employee record settings</t>
+          <t>Employee record settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>iCIMS Settings / iCIMS settings</t>
+          <t>iCIMS settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Payworks Settings / Payworks settings</t>
+          <t>Payworks settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lifecycle Operations / Lifecycle operations</t>
+          <t>Lifecycle operations</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Create Settings / Create settings</t>
+          <t>Create settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Update Settings / Update settings</t>
+          <t>Update settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Delete Settings / Termination settings</t>
+          <t>Termination settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Operation Settings / Operation settings</t>
+          <t>Operation settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Log Settings / Log settings</t>
+          <t>Log settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Report Settings / Report settings</t>
+          <t>Report settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Advance Settings / Advanced settings</t>
+          <t>Advanced settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PII &amp; Security / Data protection</t>
+          <t>Data protection</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Settings / Retry settings</t>
+          <t>Retry settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Notification / Notifications</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Notification Recipients / Notification recipients</t>
+          <t>Notification recipients</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Execution Success Notification / Execution success notification</t>
+          <t>Execution success notification</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Execution Failure Notification / Execution failure notification</t>
+          <t>Execution failure notification</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Notification Report Settings / Notification report settings</t>
+          <t>Notification report settings</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
